--- a/Analise_Graficos.xlsx
+++ b/Analise_Graficos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafae\OneDrive\Documentos\João Oliveira\Portfolio\Preço_dos_Carros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F358F01-6995-4A78-8CCF-D1A1DD012689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61FFB78D-5134-4291-A754-46D3BC00D650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,16 +22,11 @@
     <sheet name="Planilha3" sheetId="4" r:id="rId7"/>
     <sheet name="Gráficos" sheetId="6" r:id="rId8"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Planilha2!$A$9:$B$14</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Planilha2!$C$8</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Planilha2!$C$9:$C$14</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="18" r:id="rId9"/>
-    <pivotCache cacheId="23" r:id="rId10"/>
-    <pivotCache cacheId="34" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId10"/>
+    <pivotCache cacheId="2" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -56,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="128">
   <si>
     <t>ID Carro</t>
   </si>
@@ -585,31 +580,6 @@
   </cellStyles>
   <dxfs count="13">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -698,13 +668,29 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
@@ -714,6 +700,15 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1097,7 +1092,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Gráficos_Carros.xlsx]Planilha6!Tabela dinâmica12</c:name>
+    <c:name>[Analise_Graficos.xlsx]Planilha6!Tabela dinâmica12</c:name>
     <c:fmtId val="12"/>
   </c:pivotSource>
   <c:chart>
@@ -1121,14 +1116,11 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="pt-BR" sz="1600" b="1"/>
-              <a:t>Preço x</a:t>
+              <a:rPr lang="pt-BR" sz="1600" b="1" i="1">
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>PREÇO POR TIPO DE CÂMBIO</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="pt-BR" sz="1600" b="1" baseline="0"/>
-              <a:t> Tipo de Câmbio</a:t>
-            </a:r>
-            <a:endParaRPr lang="pt-BR" sz="1600" b="1"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1529,14 +1521,14 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
                       <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
@@ -1586,14 +1578,14 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
                       <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
@@ -1643,14 +1635,14 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
                       <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
@@ -1716,14 +1708,14 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
@@ -1833,14 +1825,14 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
@@ -1950,14 +1942,14 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
@@ -2078,7 +2070,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -2137,7 +2129,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -2282,14 +2274,20 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="pt-BR"/>
+              <a:rPr lang="pt-BR">
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+              </a:rPr>
               <a:t>VALOR</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="pt-BR" baseline="0"/>
+              <a:rPr lang="pt-BR" baseline="0">
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+              </a:rPr>
               <a:t> POR MARCA/MODELO E KM</a:t>
             </a:r>
-            <a:endParaRPr lang="pt-BR"/>
+            <a:endParaRPr lang="pt-BR">
+              <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -3087,14 +3085,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -3138,14 +3136,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -3180,14 +3178,14 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -3268,13 +3266,15 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1"/>
+              <a:rPr lang="en-US" sz="1600" b="1">
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+              </a:rPr>
               <a:t>PREÇO MÉDIO POR MARCA</a:t>
             </a:r>
           </a:p>
@@ -3300,7 +3300,7 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -3443,14 +3443,14 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
@@ -3572,14 +3572,14 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -3734,6 +3734,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-4F7B-448C-AA9F-F297DEFA5FFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -3749,6 +3754,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-4F7B-448C-AA9F-F297DEFA5FFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -3764,6 +3774,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-4F7B-448C-AA9F-F297DEFA5FFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -3779,6 +3794,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-4F7B-448C-AA9F-F297DEFA5FFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -3794,6 +3814,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-4F7B-448C-AA9F-F297DEFA5FFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -4013,7 +4038,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Gráficos_Carros.xlsx]Planilha6!Tabela dinâmica12</c:name>
+    <c:name>[Analise_Graficos.xlsx]Planilha6!Tabela dinâmica12</c:name>
     <c:fmtId val="9"/>
   </c:pivotSource>
   <c:chart>
@@ -5853,7 +5878,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Gráficos_Carros.xlsx]Grafico de Linhas!Tabela dinâmica11</c:name>
+    <c:name>[Analise_Graficos.xlsx]Grafico de Linhas!Tabela dinâmica11</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -8749,9 +8774,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Grafico de Linhas'!$A$5:$A$26</c:f>
+              <c:f>'Grafico de Linhas'!$A$5:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8783,36 +8808,45 @@
                   <c:v>2009</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>2011</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="23">
                   <c:v>2023</c:v>
                 </c:pt>
               </c:strCache>
@@ -8820,10 +8854,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Grafico de Linhas'!$B$5:$B$26</c:f>
+              <c:f>'Grafico de Linhas'!$B$5:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>82508.31</c:v>
                 </c:pt>
@@ -8848,25 +8882,25 @@
                 <c:pt idx="9">
                   <c:v>78461.240000000005</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>81520</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>54345.82</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>47860.7</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>41286.980000000003</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>71916.679999999993</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="22">
                   <c:v>67285.38</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="23">
                   <c:v>34979.46</c:v>
                 </c:pt>
               </c:numCache>
@@ -8888,7 +8922,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2.0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8907,9 +8941,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Grafico de Linhas'!$A$5:$A$26</c:f>
+              <c:f>'Grafico de Linhas'!$A$5:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8941,36 +8975,45 @@
                   <c:v>2009</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>2011</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="23">
                   <c:v>2023</c:v>
                 </c:pt>
               </c:strCache>
@@ -8978,72 +9021,66 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Grafico de Linhas'!$C$5:$C$26</c:f>
+              <c:f>'Grafico de Linhas'!$C$5:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>16615.919999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>49898.25</c:v>
-                </c:pt>
+                <c:ptCount val="24"/>
                 <c:pt idx="2">
-                  <c:v>75259.11</c:v>
+                  <c:v>78846.679999999993</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>50531.99</c:v>
+                  <c:v>14406.85</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>45202.62</c:v>
+                  <c:v>21213.61</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>62080.03</c:v>
+                  <c:v>60748.62</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>63401.95</c:v>
+                  <c:v>35790.559999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>75448.009999999995</c:v>
+                  <c:v>58378.37</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>59216.24</c:v>
+                  <c:v>46094.559999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19665.5</c:v>
+                  <c:v>24729.35</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>63025.14</c:v>
+                  <c:v>58426.18</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>56813.81</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>34912.74</c:v>
+                  <c:v>65248.06</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>41514.769999999997</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>48814.21</c:v>
+                  <c:v>50372.05</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>85080.44</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>10848.09</c:v>
+                  <c:v>71335.58</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>63713.279999999999</c:v>
+                  <c:v>54173</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>47700.62</c:v>
+                  <c:v>93862.62</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>28729.5</c:v>
+                  <c:v>61950.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>38267.99</c:v>
+                  <c:v>55076.77</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>60556.19</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>59779.34</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>15983.13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9052,6 +9089,191 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000003D-C19A-4AC8-929F-D60685D4C4C9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Grafico de Linhas'!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Grafico de Linhas'!$A$5:$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Grafico de Linhas'!$D$5:$D$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>16615.919999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>49898.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>75259.11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50531.99</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45202.62</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>62080.03</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>63401.95</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75448.009999999995</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>59216.24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19665.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>63025.14</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>56813.81</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>34912.74</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>41514.769999999997</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>48814.21</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>85080.44</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10848.09</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>63713.279999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>47700.62</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>28729.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>38267.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9619-44E9-BB6F-32FE42801CE5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9287,10 +9509,85 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Gráficos_Carros.xlsx]Grafico de Linhas!Tabela dinâmica11</c:name>
+    <c:name>[Analise_Graficos.xlsx]Grafico de Linhas!Tabela dinâmica11</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="1" baseline="0">
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>VARIAÇÃO DO PREÇO DOS CARROS ATRAVÉS DOS ANOS POR TIPO DE CÂMBIO</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="l">
+              <a:defRPr>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR">
+              <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.19532789928352556"/>
+          <c:y val="1.0979019779390323E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:pivotFmts>
       <c:pivotFmt>
@@ -12588,6 +12885,2694 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="56"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="57"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="58"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="59"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="60"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="61"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="62"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="63"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="64"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="65"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="66"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="67"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="68"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="69"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="70"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="71"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="72"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="73"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="74"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="75"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="76"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="77"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="78"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="79"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="80"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="81"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="82"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="83"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="84"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="85"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="86"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="87"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="88"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="89"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="90"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="91"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="92"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="93"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="94"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="95"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="96"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="97"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="98"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="99"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="100"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="101"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="102"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="103"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout>
@@ -12632,9 +15617,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Grafico de Linhas'!$A$5:$A$26</c:f>
+              <c:f>'Grafico de Linhas'!$A$5:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12666,36 +15651,45 @@
                   <c:v>2009</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>2011</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="23">
                   <c:v>2023</c:v>
                 </c:pt>
               </c:strCache>
@@ -12703,10 +15697,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Grafico de Linhas'!$B$5:$B$26</c:f>
+              <c:f>'Grafico de Linhas'!$B$5:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>82508.31</c:v>
                 </c:pt>
@@ -12731,25 +15725,25 @@
                 <c:pt idx="9">
                   <c:v>78461.240000000005</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>81520</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>54345.82</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>47860.7</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>41286.980000000003</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>71916.679999999993</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="22">
                   <c:v>67285.38</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="23">
                   <c:v>34979.46</c:v>
                 </c:pt>
               </c:numCache>
@@ -12771,7 +15765,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2.0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -12790,9 +15784,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Grafico de Linhas'!$A$5:$A$26</c:f>
+              <c:f>'Grafico de Linhas'!$A$5:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12824,36 +15818,45 @@
                   <c:v>2009</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>2011</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="23">
                   <c:v>2023</c:v>
                 </c:pt>
               </c:strCache>
@@ -12861,72 +15864,66 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Grafico de Linhas'!$C$5:$C$26</c:f>
+              <c:f>'Grafico de Linhas'!$C$5:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>16615.919999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>49898.25</c:v>
-                </c:pt>
+                <c:ptCount val="24"/>
                 <c:pt idx="2">
-                  <c:v>75259.11</c:v>
+                  <c:v>78846.679999999993</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>50531.99</c:v>
+                  <c:v>14406.85</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>45202.62</c:v>
+                  <c:v>21213.61</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>62080.03</c:v>
+                  <c:v>60748.62</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>63401.95</c:v>
+                  <c:v>35790.559999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>75448.009999999995</c:v>
+                  <c:v>58378.37</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>59216.24</c:v>
+                  <c:v>46094.559999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19665.5</c:v>
+                  <c:v>24729.35</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>63025.14</c:v>
+                  <c:v>58426.18</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>56813.81</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>34912.74</c:v>
+                  <c:v>65248.06</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>41514.769999999997</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>48814.21</c:v>
+                  <c:v>50372.05</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>85080.44</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>10848.09</c:v>
+                  <c:v>71335.58</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>63713.279999999999</c:v>
+                  <c:v>54173</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>47700.62</c:v>
+                  <c:v>93862.62</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>28729.5</c:v>
+                  <c:v>61950.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>38267.99</c:v>
+                  <c:v>55076.77</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>60556.19</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>59779.34</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>15983.13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12935,6 +15932,191 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-3763-4516-9F4B-AB16C422608C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Grafico de Linhas'!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Grafico de Linhas'!$A$5:$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Grafico de Linhas'!$D$5:$D$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>16615.919999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>49898.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>75259.11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50531.99</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45202.62</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>62080.03</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>63401.95</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75448.009999999995</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>59216.24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19665.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>63025.14</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>56813.81</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>34912.74</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>41514.769999999997</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>48814.21</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>85080.44</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10848.09</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>63713.279999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>47700.62</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>28729.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>38267.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2586-4A19-AC96-05C01AD4BF80}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12979,14 +16161,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -13038,14 +16220,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -13080,14 +16262,14 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -13171,6 +16353,33 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" b="1" i="1">
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>Total Carros</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13184,7 +16393,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -13240,17 +16449,20 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
@@ -13271,13 +16483,14 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525">
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
                       <a:solidFill>
                         <a:schemeClr val="tx1">
                           <a:lumMod val="35000"/>
                           <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
+                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -13285,6 +16498,20 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Planilha1!$A$2:$A$6</c:f>
@@ -13347,8 +16574,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="444"/>
-        <c:overlap val="-90"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
         <c:axId val="1875720351"/>
         <c:axId val="1875719871"/>
       </c:barChart>
@@ -13359,20 +16586,72 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1400" b="1">
+                    <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>Marcas</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1400" b="1" baseline="0">
+                    <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t> dos Carros</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1400" b="1">
+                  <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
           <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-        </c:majorGridlines>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -13395,14 +16674,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -13422,12 +16701,114 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1100" b="1">
+                    <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>Qtd</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>.</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="1875720351"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -13453,7 +16834,7 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -13512,20 +16893,26 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1"/>
+              <a:rPr lang="en-US" sz="1600" b="1">
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+              </a:rPr>
               <a:t>PREÇO</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1" baseline="0"/>
+              <a:rPr lang="en-US" sz="1600" b="1" baseline="0">
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+              </a:rPr>
               <a:t> MÉDIO POR KM</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" sz="1600" b="1"/>
+            <a:endParaRPr lang="en-US" sz="1600" b="1">
+              <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -13549,7 +16936,7 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -13604,14 +16991,14 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
@@ -13647,6 +17034,20 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>Planilha2!$A$21:$A$23</c:f>
@@ -13730,14 +17131,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -13757,7 +17158,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
@@ -13777,33 +17178,6 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="694975456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -19488,7 +22862,7 @@
 </file>
 
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -19499,7 +22873,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -19522,18 +22896,18 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="bg1"/>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
@@ -19545,7 +22919,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -19553,14 +22927,11 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -19592,45 +22963,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="22225" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -19642,34 +23003,30 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -19691,13 +23048,15 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -19712,15 +23071,15 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -19731,16 +23090,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -19749,10 +23109,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
@@ -19768,15 +23128,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -19795,16 +23161,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="5000"/>
             <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -19813,16 +23180,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -19831,16 +23199,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -19861,7 +23230,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
@@ -19869,7 +23238,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -19882,17 +23251,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -19900,10 +23258,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
@@ -19924,7 +23282,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -19933,14 +23291,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDash"/>
+        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -19954,7 +23312,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="800" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
@@ -19970,8 +23328,8 @@
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -19987,17 +23345,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -20005,8 +23352,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -20876,15 +24229,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>514349</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>438149</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -27082,7 +30435,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4674B691-8FDC-45DF-B566-D3E58BE161E2}" name="Tabela dinâmica12" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4674B691-8FDC-45DF-B566-D3E58BE161E2}" name="Tabela dinâmica12" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="25">
   <location ref="A3:E7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -27137,7 +30490,7 @@
     <dataField name="Média de Preço Médio" fld="2" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="7">
+    <format dxfId="12">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
@@ -27232,7 +30585,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{77489171-7DB1-4CAC-87CB-899A01DD15CD}" name="Tabela dinâmica14" cacheId="34" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{77489171-7DB1-4CAC-87CB-899A01DD15CD}" name="Tabela dinâmica14" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:AD8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisCol" showAll="0">
@@ -27392,10 +30745,10 @@
     <dataField name="Soma de Preço Medio" fld="2" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="9">
+    <format dxfId="11">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -27412,8 +30765,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{19DE18E2-8A0D-40AF-98A3-90E7698405A5}" name="Tabela dinâmica11" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A3:D26" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{19DE18E2-8A0D-40AF-98A3-90E7698405A5}" name="Tabela dinâmica11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="A3:E29" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
       <items count="25">
@@ -27453,7 +30806,7 @@
         <item h="1" x="22"/>
         <item h="1" x="28"/>
         <item h="1" x="16"/>
-        <item h="1" x="44"/>
+        <item x="44"/>
         <item h="1" x="46"/>
         <item h="1" x="7"/>
         <item h="1" x="39"/>
@@ -27505,7 +30858,7 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="22">
+  <rowItems count="25">
     <i>
       <x/>
     </i>
@@ -27537,10 +30890,16 @@
       <x v="9"/>
     </i>
     <i>
+      <x v="10"/>
+    </i>
+    <i>
       <x v="11"/>
     </i>
     <i>
       <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
     </i>
     <i>
       <x v="14"/>
@@ -27564,6 +30923,9 @@
       <x v="20"/>
     </i>
     <i>
+      <x v="21"/>
+    </i>
+    <i>
       <x v="22"/>
     </i>
     <i>
@@ -27576,9 +30938,12 @@
   <colFields count="1">
     <field x="2"/>
   </colFields>
-  <colItems count="3">
+  <colItems count="4">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="6"/>
     </i>
     <i>
       <x v="10"/>
@@ -27590,7 +30955,7 @@
   <dataFields count="1">
     <dataField name="Média de Preço Médio" fld="1" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="54">
+  <chartFormats count="102">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
@@ -28239,6 +31604,582 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="3" format="56" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="57" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="58" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="59" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="60" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="61" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="62" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="63" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="64" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="65" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="66" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="67" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="68" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="69" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="70" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="71" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="72" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="73" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="21"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="74" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="22"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="75" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="23"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="76" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="24"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="77" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="25"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="78" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="26"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="79" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="27"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="80" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="28"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="81" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="29"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="82" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="30"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="83" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="31"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="84" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="32"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="85" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="33"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="86" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="34"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="87" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="35"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="88" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="36"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="89" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="37"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="90" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="38"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="91" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="39"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="92" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="40"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="93" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="41"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="94" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="42"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="95" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="43"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="96" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="44"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="97" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="45"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="98" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="46"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="99" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="47"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="100" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="48"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="101" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="49"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="102" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="50"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="103" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -28256,20 +32197,20 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6272AA82-F425-4D1F-ACFA-5712460504D8}" name="Tabela1" displayName="Tabela1" ref="A1:C2" totalsRowShown="0">
   <autoFilter ref="A1:C2" xr:uid="{6272AA82-F425-4D1F-ACFA-5712460504D8}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{CC0693FE-4402-45D9-83B3-EB1B098AFE20}" name="Preço medio" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{21B9CCF0-2623-4547-B217-73E255AFB456}" name="Preço Maximo" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{0F1DE2F4-B4BE-45A8-A495-61A21B8712A8}" name="Preco Mínimo" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{CC0693FE-4402-45D9-83B3-EB1B098AFE20}" name="Preço medio" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{21B9CCF0-2623-4547-B217-73E255AFB456}" name="Preço Maximo" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{0F1DE2F4-B4BE-45A8-A495-61A21B8712A8}" name="Preco Mínimo" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A3B24BFF-F31D-4674-9614-1B35D814B0E4}" name="Tabela13" displayName="Tabela13" ref="F2:H3" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A3B24BFF-F31D-4674-9614-1B35D814B0E4}" name="Tabela13" displayName="Tabela13" ref="F2:H3" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{65C1D02F-F0D2-419E-8045-0CB6618139CE}" name="Média de Valor dos Carros" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{E27BC327-7A59-43CC-A576-632A416582B5}" name="Maior Valor de um Carro" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{660AFE7D-4D99-48D7-8827-FC53B4064BD1}" name="Menor Valor de um Carro" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{65C1D02F-F0D2-419E-8045-0CB6618139CE}" name="Média de Valor dos Carros" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{E27BC327-7A59-43CC-A576-632A416582B5}" name="Maior Valor de um Carro" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{660AFE7D-4D99-48D7-8827-FC53B4064BD1}" name="Menor Valor de um Carro" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -31085,7 +35026,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D212C53A-549F-4581-A5B8-23797679EC72}">
-  <dimension ref="A3:D26"/>
+  <dimension ref="A3:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
@@ -31110,7 +35051,7 @@
     <col min="52" max="53" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>86</v>
       </c>
@@ -31118,7 +35059,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>83</v>
       </c>
@@ -31126,41 +35067,46 @@
         <v>82</v>
       </c>
       <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" t="s">
         <v>52</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2000</v>
       </c>
       <c r="B5" s="5">
         <v>82508.31</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5">
         <v>16615.919999999998</v>
       </c>
-      <c r="D5" s="5">
+      <c r="E5" s="5">
         <v>49562.114999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2001</v>
       </c>
       <c r="B6" s="5">
         <v>48934.71</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5">
         <v>49898.25</v>
       </c>
-      <c r="D6" s="5">
+      <c r="E6" s="5">
         <v>49416.479999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2002</v>
       </c>
@@ -31168,13 +35114,16 @@
         <v>82335.210000000006</v>
       </c>
       <c r="C7" s="5">
+        <v>78846.679999999993</v>
+      </c>
+      <c r="D7" s="5">
         <v>75259.11</v>
       </c>
-      <c r="D7" s="5">
-        <v>78797.16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="5">
+        <v>78813.666666666672</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>2003</v>
       </c>
@@ -31182,13 +35131,16 @@
         <v>55755.47</v>
       </c>
       <c r="C8" s="5">
+        <v>14406.85</v>
+      </c>
+      <c r="D8" s="5">
         <v>50531.99</v>
       </c>
-      <c r="D8" s="5">
-        <v>53143.729999999996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="5">
+        <v>40231.436666666668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2004</v>
       </c>
@@ -31196,25 +35148,31 @@
         <v>72763.38</v>
       </c>
       <c r="C9" s="5">
+        <v>21213.61</v>
+      </c>
+      <c r="D9" s="5">
         <v>45202.62</v>
       </c>
-      <c r="D9" s="5">
-        <v>58983</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="5">
+        <v>46393.203333333338</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>2005</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>62080.03</v>
+        <v>60748.62</v>
       </c>
       <c r="D10" s="5">
         <v>62080.03</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="5">
+        <v>61414.324999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>2006</v>
       </c>
@@ -31222,13 +35180,16 @@
         <v>69924.53</v>
       </c>
       <c r="C11" s="5">
+        <v>35790.559999999998</v>
+      </c>
+      <c r="D11" s="5">
         <v>63401.95</v>
       </c>
-      <c r="D11" s="5">
-        <v>66663.239999999991</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="5">
+        <v>56372.346666666657</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>2007</v>
       </c>
@@ -31236,25 +35197,31 @@
         <v>61503.74</v>
       </c>
       <c r="C12" s="5">
+        <v>58378.37</v>
+      </c>
+      <c r="D12" s="5">
         <v>75448.009999999995</v>
       </c>
-      <c r="D12" s="5">
-        <v>68475.875</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="5">
+        <v>65110.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>2008</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>59216.24</v>
+        <v>46094.559999999998</v>
       </c>
       <c r="D13" s="5">
         <v>59216.24</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="5">
+        <v>52655.399999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>2009</v>
       </c>
@@ -31262,170 +35229,242 @@
         <v>78461.240000000005</v>
       </c>
       <c r="C14" s="5">
+        <v>24729.35</v>
+      </c>
+      <c r="D14" s="5">
         <v>19665.5</v>
       </c>
-      <c r="D14" s="5">
-        <v>49063.37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="5">
+        <v>40952.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
+        <v>58426.18</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5">
+        <v>58426.18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>2011</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5">
+        <v>65248.06</v>
+      </c>
+      <c r="D16" s="5">
         <v>63025.14</v>
       </c>
-      <c r="D15" s="5">
-        <v>63025.14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+      <c r="E16" s="5">
+        <v>64136.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>2012</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B17" s="5">
         <v>81520</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5">
         <v>56813.81</v>
       </c>
-      <c r="D16" s="5">
+      <c r="E17" s="5">
         <v>69166.904999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>2014</v>
-      </c>
-      <c r="B17" s="5">
-        <v>54345.82</v>
-      </c>
-      <c r="C17" s="5">
-        <v>34912.74</v>
-      </c>
-      <c r="D17" s="5">
-        <v>44629.279999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>41514.769999999997</v>
-      </c>
-      <c r="D18" s="5">
-        <v>41514.769999999997</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50372.05</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5">
+        <v>50372.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B19" s="5">
-        <v>47860.7</v>
-      </c>
-      <c r="C19" s="5">
-        <v>48814.21</v>
-      </c>
+        <v>54345.82</v>
+      </c>
+      <c r="C19" s="5"/>
       <c r="D19" s="5">
-        <v>48337.455000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34912.74</v>
+      </c>
+      <c r="E19" s="5">
+        <v>44629.279999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>85080.44</v>
+        <v>71335.58</v>
       </c>
       <c r="D20" s="5">
-        <v>85080.44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41514.769999999997</v>
+      </c>
+      <c r="E20" s="5">
+        <v>56425.175000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B21" s="5">
-        <v>41286.980000000003</v>
-      </c>
-      <c r="C21" s="5">
-        <v>10848.09</v>
-      </c>
+        <v>47860.7</v>
+      </c>
+      <c r="C21" s="5"/>
       <c r="D21" s="5">
-        <v>26067.535000000003</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48814.21</v>
+      </c>
+      <c r="E21" s="5">
+        <v>48337.455000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
+        <v>54173</v>
+      </c>
+      <c r="D22" s="5">
+        <v>85080.44</v>
+      </c>
+      <c r="E22" s="5">
+        <v>69626.720000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>2018</v>
+      </c>
+      <c r="B23" s="5">
+        <v>41286.980000000003</v>
+      </c>
+      <c r="C23" s="5">
+        <v>93862.62</v>
+      </c>
+      <c r="D23" s="5">
+        <v>10848.09</v>
+      </c>
+      <c r="E23" s="5">
+        <v>48665.896666666667</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5">
+        <v>61950.6</v>
+      </c>
+      <c r="D24" s="5">
         <v>63713.279999999999</v>
       </c>
-      <c r="D22" s="5">
-        <v>63713.279999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+      <c r="E24" s="5">
+        <v>62831.94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>2020</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B25" s="5">
         <v>71916.679999999993</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C25" s="5">
+        <v>55076.77</v>
+      </c>
+      <c r="D25" s="5">
         <v>47700.62</v>
       </c>
-      <c r="D23" s="5">
-        <v>59808.649999999994</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+      <c r="E25" s="5">
+        <v>58231.356666666659</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5">
+        <v>60556.19</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5">
+        <v>60556.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
         <v>2022</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B27" s="5">
         <v>67285.38</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C27" s="5">
+        <v>59779.34</v>
+      </c>
+      <c r="D27" s="5">
         <v>28729.5</v>
       </c>
-      <c r="D24" s="5">
-        <v>48007.44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+      <c r="E27" s="5">
+        <v>51931.406666666669</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>2023</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B28" s="5">
         <v>34979.46</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C28" s="5">
+        <v>15983.13</v>
+      </c>
+      <c r="D28" s="5">
         <v>38267.99</v>
       </c>
-      <c r="D25" s="5">
-        <v>36623.724999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="E28" s="5">
+        <v>29743.526666666661</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B29" s="5">
         <v>63425.440666666647</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C29" s="5">
+        <v>51945.901052631576</v>
+      </c>
+      <c r="D29" s="5">
         <v>49368.58142857143</v>
       </c>
-      <c r="D26" s="5">
-        <v>55225.606111111112</v>
+      <c r="E29" s="5">
+        <v>54092.617090909087</v>
       </c>
     </row>
   </sheetData>

--- a/Analise_Graficos.xlsx
+++ b/Analise_Graficos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafae\OneDrive\Documentos\João Oliveira\Portfolio\Preço_dos_Carros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61FFB78D-5134-4291-A754-46D3BC00D650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D93087-898F-4054-AB80-12ED774F6631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trad" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="130">
   <si>
     <t>ID Carro</t>
   </si>
@@ -436,6 +436,12 @@
   <si>
     <t>Média de Valor dos Carros</t>
   </si>
+  <si>
+    <t>Preco Medio</t>
+  </si>
+  <si>
+    <t>QTD</t>
+  </si>
 </sst>
 </file>
 
@@ -445,7 +451,7 @@
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -461,8 +467,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -473,6 +486,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -556,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -574,6 +593,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5943,6 +5971,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5999,6 +6030,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6055,6 +6089,9 @@
       <c:pivotFmt>
         <c:idx val="3"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6111,6 +6148,9 @@
       <c:pivotFmt>
         <c:idx val="4"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6167,6 +6207,9 @@
       <c:pivotFmt>
         <c:idx val="5"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6279,6 +6322,9 @@
       <c:pivotFmt>
         <c:idx val="7"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6335,6 +6381,9 @@
       <c:pivotFmt>
         <c:idx val="8"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6391,6 +6440,9 @@
       <c:pivotFmt>
         <c:idx val="9"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6503,6 +6555,9 @@
       <c:pivotFmt>
         <c:idx val="11"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6559,6 +6614,9 @@
       <c:pivotFmt>
         <c:idx val="12"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6615,6 +6673,9 @@
       <c:pivotFmt>
         <c:idx val="13"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6671,6 +6732,9 @@
       <c:pivotFmt>
         <c:idx val="14"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6727,6 +6791,9 @@
       <c:pivotFmt>
         <c:idx val="15"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6783,6 +6850,9 @@
       <c:pivotFmt>
         <c:idx val="16"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6839,6 +6909,9 @@
       <c:pivotFmt>
         <c:idx val="17"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6895,6 +6968,9 @@
       <c:pivotFmt>
         <c:idx val="18"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6951,6 +7027,9 @@
       <c:pivotFmt>
         <c:idx val="19"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7007,6 +7086,9 @@
       <c:pivotFmt>
         <c:idx val="20"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7063,6 +7145,9 @@
       <c:pivotFmt>
         <c:idx val="21"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7119,6 +7204,9 @@
       <c:pivotFmt>
         <c:idx val="22"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7175,6 +7263,9 @@
       <c:pivotFmt>
         <c:idx val="23"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7231,6 +7322,9 @@
       <c:pivotFmt>
         <c:idx val="24"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7287,6 +7381,9 @@
       <c:pivotFmt>
         <c:idx val="25"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7343,6 +7440,9 @@
       <c:pivotFmt>
         <c:idx val="26"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7399,6 +7499,9 @@
       <c:pivotFmt>
         <c:idx val="27"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7455,6 +7558,9 @@
       <c:pivotFmt>
         <c:idx val="28"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7511,6 +7617,9 @@
       <c:pivotFmt>
         <c:idx val="29"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7567,6 +7676,9 @@
       <c:pivotFmt>
         <c:idx val="30"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7623,6 +7735,9 @@
       <c:pivotFmt>
         <c:idx val="31"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7679,6 +7794,9 @@
       <c:pivotFmt>
         <c:idx val="32"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7735,6 +7853,9 @@
       <c:pivotFmt>
         <c:idx val="33"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7791,6 +7912,9 @@
       <c:pivotFmt>
         <c:idx val="34"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7847,6 +7971,9 @@
       <c:pivotFmt>
         <c:idx val="35"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7903,6 +8030,9 @@
       <c:pivotFmt>
         <c:idx val="36"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7959,6 +8089,9 @@
       <c:pivotFmt>
         <c:idx val="37"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8015,6 +8148,9 @@
       <c:pivotFmt>
         <c:idx val="38"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8071,6 +8207,9 @@
       <c:pivotFmt>
         <c:idx val="39"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8127,6 +8266,9 @@
       <c:pivotFmt>
         <c:idx val="40"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8183,6 +8325,9 @@
       <c:pivotFmt>
         <c:idx val="41"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8239,6 +8384,9 @@
       <c:pivotFmt>
         <c:idx val="42"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8295,6 +8443,9 @@
       <c:pivotFmt>
         <c:idx val="43"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8351,6 +8502,9 @@
       <c:pivotFmt>
         <c:idx val="44"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8407,6 +8561,9 @@
       <c:pivotFmt>
         <c:idx val="45"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8463,6 +8620,9 @@
       <c:pivotFmt>
         <c:idx val="46"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8519,6 +8679,9 @@
       <c:pivotFmt>
         <c:idx val="47"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8575,6 +8738,9 @@
       <c:pivotFmt>
         <c:idx val="48"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8631,6 +8797,9 @@
       <c:pivotFmt>
         <c:idx val="49"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -8687,6 +8856,9 @@
       <c:pivotFmt>
         <c:idx val="50"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -12776,6 +12948,9 @@
       <c:pivotFmt>
         <c:idx val="54"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -12888,6 +13063,9 @@
       <c:pivotFmt>
         <c:idx val="56"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -12944,6 +13122,9 @@
       <c:pivotFmt>
         <c:idx val="57"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13000,6 +13181,9 @@
       <c:pivotFmt>
         <c:idx val="58"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13112,6 +13296,9 @@
       <c:pivotFmt>
         <c:idx val="60"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13168,6 +13355,9 @@
       <c:pivotFmt>
         <c:idx val="61"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13224,6 +13414,9 @@
       <c:pivotFmt>
         <c:idx val="62"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13280,6 +13473,9 @@
       <c:pivotFmt>
         <c:idx val="63"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13336,6 +13532,9 @@
       <c:pivotFmt>
         <c:idx val="64"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13392,6 +13591,9 @@
       <c:pivotFmt>
         <c:idx val="65"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13448,6 +13650,9 @@
       <c:pivotFmt>
         <c:idx val="66"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13504,6 +13709,9 @@
       <c:pivotFmt>
         <c:idx val="67"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13560,6 +13768,9 @@
       <c:pivotFmt>
         <c:idx val="68"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13616,6 +13827,9 @@
       <c:pivotFmt>
         <c:idx val="69"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13672,6 +13886,9 @@
       <c:pivotFmt>
         <c:idx val="70"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13728,6 +13945,9 @@
       <c:pivotFmt>
         <c:idx val="71"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13784,6 +14004,9 @@
       <c:pivotFmt>
         <c:idx val="72"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13840,6 +14063,9 @@
       <c:pivotFmt>
         <c:idx val="73"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13896,6 +14122,9 @@
       <c:pivotFmt>
         <c:idx val="74"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -13952,6 +14181,9 @@
       <c:pivotFmt>
         <c:idx val="75"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14008,6 +14240,9 @@
       <c:pivotFmt>
         <c:idx val="76"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14064,6 +14299,9 @@
       <c:pivotFmt>
         <c:idx val="77"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14120,6 +14358,9 @@
       <c:pivotFmt>
         <c:idx val="78"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14176,6 +14417,9 @@
       <c:pivotFmt>
         <c:idx val="79"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14232,6 +14476,9 @@
       <c:pivotFmt>
         <c:idx val="80"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14288,6 +14535,9 @@
       <c:pivotFmt>
         <c:idx val="81"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14344,6 +14594,9 @@
       <c:pivotFmt>
         <c:idx val="82"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14400,6 +14653,9 @@
       <c:pivotFmt>
         <c:idx val="83"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14456,6 +14712,9 @@
       <c:pivotFmt>
         <c:idx val="84"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14512,6 +14771,9 @@
       <c:pivotFmt>
         <c:idx val="85"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14568,6 +14830,9 @@
       <c:pivotFmt>
         <c:idx val="86"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14624,6 +14889,9 @@
       <c:pivotFmt>
         <c:idx val="87"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14680,6 +14948,9 @@
       <c:pivotFmt>
         <c:idx val="88"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14736,6 +15007,9 @@
       <c:pivotFmt>
         <c:idx val="89"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14792,6 +15066,9 @@
       <c:pivotFmt>
         <c:idx val="90"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14848,6 +15125,9 @@
       <c:pivotFmt>
         <c:idx val="91"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14904,6 +15184,9 @@
       <c:pivotFmt>
         <c:idx val="92"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -14960,6 +15243,9 @@
       <c:pivotFmt>
         <c:idx val="93"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -15016,6 +15302,9 @@
       <c:pivotFmt>
         <c:idx val="94"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -15072,6 +15361,9 @@
       <c:pivotFmt>
         <c:idx val="95"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -15128,6 +15420,9 @@
       <c:pivotFmt>
         <c:idx val="96"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -15184,6 +15479,9 @@
       <c:pivotFmt>
         <c:idx val="97"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -15240,6 +15538,9 @@
       <c:pivotFmt>
         <c:idx val="98"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -15296,6 +15597,9 @@
       <c:pivotFmt>
         <c:idx val="99"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -15352,6 +15656,9 @@
       <c:pivotFmt>
         <c:idx val="100"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -15408,6 +15715,9 @@
       <c:pivotFmt>
         <c:idx val="101"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -15464,6 +15774,9 @@
       <c:pivotFmt>
         <c:idx val="102"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -15520,6 +15833,9 @@
       <c:pivotFmt>
         <c:idx val="103"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -32636,7 +32952,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109E1C2A-721A-4280-B812-D51065658051}">
-  <dimension ref="A3:E7"/>
+  <dimension ref="A3:E32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
@@ -32718,6 +33034,50 @@
       </c>
       <c r="E7" s="5">
         <v>52629.885000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="15">
+        <v>52785.91</v>
+      </c>
+      <c r="C30" s="14">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="15">
+        <v>52249.42</v>
+      </c>
+      <c r="C31" s="14">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="15">
+        <v>51738.71</v>
+      </c>
+      <c r="C32" s="14">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
